--- a/AAII_Financials/Quarterly/ZCMD_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ZCMD_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="369" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="377" uniqueCount="92">
   <si>
     <t>ZCMD</t>
   </si>
@@ -662,7 +662,12 @@
     <col min="1" max="1" width="8" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
@@ -697,19 +702,19 @@
         <v>45930</v>
       </c>
       <c r="F7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="G7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="H7" s="2">
         <v>45657</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45565</v>
       </c>
-      <c r="H7" s="2">
-        <v>45291</v>
-      </c>
-      <c r="I7" s="2">
-        <v>45199</v>
-      </c>
       <c r="J7" s="2">
-        <v>44926</v>
+        <v>45473</v>
       </c>
       <c r="K7" s="2">
         <v>44834</v>
@@ -768,19 +773,19 @@
         <v>2900</v>
       </c>
       <c r="F8" s="3">
+        <v>2800</v>
+      </c>
+      <c r="G8" s="3">
+        <v>2800</v>
+      </c>
+      <c r="H8" s="3">
         <v>3800</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>3800</v>
       </c>
-      <c r="H8" s="3">
-        <v>4500</v>
-      </c>
-      <c r="I8" s="3">
-        <v>4500</v>
-      </c>
       <c r="J8" s="3">
-        <v>3400</v>
+        <v>4200</v>
       </c>
       <c r="K8" s="3">
         <v>3400</v>
@@ -839,19 +844,19 @@
         <v>1700</v>
       </c>
       <c r="F9" s="3">
+        <v>1400</v>
+      </c>
+      <c r="G9" s="3">
+        <v>1400</v>
+      </c>
+      <c r="H9" s="3">
         <v>1700</v>
       </c>
-      <c r="G9" s="3">
+      <c r="I9" s="3">
         <v>1700</v>
       </c>
-      <c r="H9" s="3">
-        <v>2400</v>
-      </c>
-      <c r="I9" s="3">
-        <v>2400</v>
-      </c>
       <c r="J9" s="3">
-        <v>2800</v>
+        <v>1800</v>
       </c>
       <c r="K9" s="3">
         <v>2800</v>
@@ -910,10 +915,10 @@
         <v>1200</v>
       </c>
       <c r="F10" s="3">
-        <v>2100</v>
+        <v>1400</v>
       </c>
       <c r="G10" s="3">
-        <v>2100</v>
+        <v>1400</v>
       </c>
       <c r="H10" s="3">
         <v>2100</v>
@@ -922,7 +927,7 @@
         <v>2100</v>
       </c>
       <c r="J10" s="3">
-        <v>600</v>
+        <v>2400</v>
       </c>
       <c r="K10" s="3">
         <v>600</v>
@@ -1008,10 +1013,10 @@
         <v>0</v>
       </c>
       <c r="F12" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G12" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H12" s="3">
         <v>100</v>
@@ -1149,20 +1154,20 @@
       <c r="E14" s="3">
         <v>0</v>
       </c>
-      <c r="F14" s="3">
+      <c r="F14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H14" s="3">
         <v>-100</v>
       </c>
-      <c r="G14" s="3">
+      <c r="I14" s="3">
         <v>-100</v>
       </c>
-      <c r="H14" s="3">
-        <v>3200</v>
-      </c>
-      <c r="I14" s="3">
-        <v>3100</v>
-      </c>
       <c r="J14" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -1233,7 +1238,7 @@
         <v>100</v>
       </c>
       <c r="J15" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K15" s="3">
         <v>100</v>
@@ -1316,19 +1321,19 @@
         <v>5500</v>
       </c>
       <c r="F17" s="3">
+        <v>3200</v>
+      </c>
+      <c r="G17" s="3">
+        <v>3200</v>
+      </c>
+      <c r="H17" s="3">
         <v>3900</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>3900</v>
       </c>
-      <c r="H17" s="3">
-        <v>5000</v>
-      </c>
-      <c r="I17" s="3">
-        <v>5000</v>
-      </c>
       <c r="J17" s="3">
-        <v>5200</v>
+        <v>4200</v>
       </c>
       <c r="K17" s="3">
         <v>5200</v>
@@ -1387,19 +1392,19 @@
         <v>-2700</v>
       </c>
       <c r="F18" s="3">
+        <v>-400</v>
+      </c>
+      <c r="G18" s="3">
+        <v>-400</v>
+      </c>
+      <c r="H18" s="3">
         <v>-100</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>-100</v>
       </c>
-      <c r="H18" s="3">
-        <v>-400</v>
-      </c>
-      <c r="I18" s="3">
-        <v>-400</v>
-      </c>
       <c r="J18" s="3">
-        <v>-1700</v>
+        <v>0</v>
       </c>
       <c r="K18" s="3">
         <v>-1700</v>
@@ -1485,19 +1490,19 @@
         <v>0</v>
       </c>
       <c r="F20" s="3">
+        <v>0</v>
+      </c>
+      <c r="G20" s="3">
+        <v>0</v>
+      </c>
+      <c r="H20" s="3">
         <v>100</v>
       </c>
-      <c r="G20" s="3">
+      <c r="I20" s="3">
         <v>100</v>
       </c>
-      <c r="H20" s="3">
-        <v>-200</v>
-      </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-100</v>
-      </c>
-      <c r="J20" s="3">
-        <v>-200</v>
       </c>
       <c r="K20" s="3">
         <v>-200</v>
@@ -1556,19 +1561,19 @@
         <v>-2600</v>
       </c>
       <c r="F21" s="3">
+        <v>-300</v>
+      </c>
+      <c r="G21" s="3">
+        <v>-300</v>
+      </c>
+      <c r="H21" s="3">
         <v>-100</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>-100</v>
       </c>
-      <c r="H21" s="3">
-        <v>-200</v>
-      </c>
-      <c r="I21" s="3">
-        <v>-200</v>
-      </c>
       <c r="J21" s="3">
-        <v>-1400</v>
+        <v>100</v>
       </c>
       <c r="K21" s="3">
         <v>-1400</v>
@@ -1698,19 +1703,19 @@
         <v>-2600</v>
       </c>
       <c r="F23" s="3">
-        <v>0</v>
+        <v>-300</v>
       </c>
       <c r="G23" s="3">
-        <v>0</v>
+        <v>-300</v>
       </c>
       <c r="H23" s="3">
-        <v>-3400</v>
+        <v>0</v>
       </c>
       <c r="I23" s="3">
-        <v>-3400</v>
+        <v>0</v>
       </c>
       <c r="J23" s="3">
-        <v>-1500</v>
+        <v>0</v>
       </c>
       <c r="K23" s="3">
         <v>-1500</v>
@@ -1769,19 +1774,19 @@
         <v>-100</v>
       </c>
       <c r="F24" s="3">
+        <v>100</v>
+      </c>
+      <c r="G24" s="3">
+        <v>100</v>
+      </c>
+      <c r="H24" s="3">
         <v>200</v>
       </c>
-      <c r="G24" s="3">
+      <c r="I24" s="3">
         <v>200</v>
       </c>
-      <c r="H24" s="3">
+      <c r="J24" s="3">
         <v>-100</v>
-      </c>
-      <c r="I24" s="3">
-        <v>-100</v>
-      </c>
-      <c r="J24" s="3">
-        <v>0</v>
       </c>
       <c r="K24" s="3">
         <v>0</v>
@@ -1911,19 +1916,19 @@
         <v>-2500</v>
       </c>
       <c r="F26" s="3">
+        <v>-400</v>
+      </c>
+      <c r="G26" s="3">
+        <v>-400</v>
+      </c>
+      <c r="H26" s="3">
         <v>-200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>-200</v>
       </c>
-      <c r="H26" s="3">
-        <v>-3300</v>
-      </c>
-      <c r="I26" s="3">
-        <v>-3300</v>
-      </c>
       <c r="J26" s="3">
-        <v>-1500</v>
+        <v>100</v>
       </c>
       <c r="K26" s="3">
         <v>-1500</v>
@@ -1982,19 +1987,19 @@
         <v>-2700</v>
       </c>
       <c r="F27" s="3">
+        <v>-500</v>
+      </c>
+      <c r="G27" s="3">
+        <v>-500</v>
+      </c>
+      <c r="H27" s="3">
         <v>-400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>-400</v>
       </c>
-      <c r="H27" s="3">
-        <v>-3300</v>
-      </c>
-      <c r="I27" s="3">
-        <v>-3300</v>
-      </c>
       <c r="J27" s="3">
-        <v>-1500</v>
+        <v>0</v>
       </c>
       <c r="K27" s="3">
         <v>-1500</v>
@@ -2337,19 +2342,19 @@
         <v>0</v>
       </c>
       <c r="F32" s="3">
+        <v>0</v>
+      </c>
+      <c r="G32" s="3">
+        <v>0</v>
+      </c>
+      <c r="H32" s="3">
         <v>-100</v>
       </c>
-      <c r="G32" s="3">
+      <c r="I32" s="3">
         <v>-100</v>
       </c>
-      <c r="H32" s="3">
-        <v>200</v>
-      </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>100</v>
-      </c>
-      <c r="J32" s="3">
-        <v>200</v>
       </c>
       <c r="K32" s="3">
         <v>200</v>
@@ -2408,19 +2413,19 @@
         <v>-2700</v>
       </c>
       <c r="F33" s="3">
+        <v>-500</v>
+      </c>
+      <c r="G33" s="3">
+        <v>-500</v>
+      </c>
+      <c r="H33" s="3">
         <v>-400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>-400</v>
       </c>
-      <c r="H33" s="3">
-        <v>-3300</v>
-      </c>
-      <c r="I33" s="3">
-        <v>-3300</v>
-      </c>
       <c r="J33" s="3">
-        <v>-1500</v>
+        <v>0</v>
       </c>
       <c r="K33" s="3">
         <v>-1500</v>
@@ -2550,19 +2555,19 @@
         <v>-2700</v>
       </c>
       <c r="F35" s="3">
+        <v>-500</v>
+      </c>
+      <c r="G35" s="3">
+        <v>-500</v>
+      </c>
+      <c r="H35" s="3">
         <v>-400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>-400</v>
       </c>
-      <c r="H35" s="3">
-        <v>-3300</v>
-      </c>
-      <c r="I35" s="3">
-        <v>-3300</v>
-      </c>
       <c r="J35" s="3">
-        <v>-1500</v>
+        <v>0</v>
       </c>
       <c r="K35" s="3">
         <v>-1500</v>
@@ -2626,19 +2631,19 @@
         <v>45930</v>
       </c>
       <c r="F38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="G38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="H38" s="2">
         <v>45657</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45565</v>
       </c>
-      <c r="H38" s="2">
-        <v>45291</v>
-      </c>
-      <c r="I38" s="2">
-        <v>45199</v>
-      </c>
       <c r="J38" s="2">
-        <v>44926</v>
+        <v>45473</v>
       </c>
       <c r="K38" s="2">
         <v>44834</v>
@@ -2751,19 +2756,19 @@
         <v>8100</v>
       </c>
       <c r="F41" s="3">
+        <v>8900</v>
+      </c>
+      <c r="G41" s="3">
+        <v>8900</v>
+      </c>
+      <c r="H41" s="3">
         <v>7800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>7800</v>
       </c>
-      <c r="H41" s="3">
-        <v>7500</v>
-      </c>
-      <c r="I41" s="3">
-        <v>7500</v>
-      </c>
       <c r="J41" s="3">
-        <v>11500</v>
+        <v>6300</v>
       </c>
       <c r="K41" s="3">
         <v>11500</v>
@@ -2822,19 +2827,19 @@
         <v>5800</v>
       </c>
       <c r="F42" s="3">
+        <v>6100</v>
+      </c>
+      <c r="G42" s="3">
+        <v>6100</v>
+      </c>
+      <c r="H42" s="3">
         <v>5200</v>
       </c>
-      <c r="G42" s="3">
+      <c r="I42" s="3">
         <v>5200</v>
       </c>
-      <c r="H42" s="3">
+      <c r="J42" s="3">
         <v>5900</v>
-      </c>
-      <c r="I42" s="3">
-        <v>5900</v>
-      </c>
-      <c r="J42" s="3">
-        <v>500</v>
       </c>
       <c r="K42" s="3">
         <v>500</v>
@@ -2893,19 +2898,19 @@
         <v>2900</v>
       </c>
       <c r="F43" s="3">
+        <v>3600</v>
+      </c>
+      <c r="G43" s="3">
+        <v>3600</v>
+      </c>
+      <c r="H43" s="3">
         <v>4800</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>4800</v>
       </c>
-      <c r="H43" s="3">
-        <v>3000</v>
-      </c>
-      <c r="I43" s="3">
-        <v>3000</v>
-      </c>
       <c r="J43" s="3">
-        <v>8900</v>
+        <v>2800</v>
       </c>
       <c r="K43" s="3">
         <v>8900</v>
@@ -2963,11 +2968,11 @@
       <c r="E44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F44" s="3">
-        <v>600</v>
-      </c>
-      <c r="G44" s="3">
-        <v>600</v>
+      <c r="F44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H44" s="3">
         <v>600</v>
@@ -2976,7 +2981,7 @@
         <v>600</v>
       </c>
       <c r="J44" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="K44" s="3">
         <v>200</v>
@@ -3035,19 +3040,19 @@
         <v>200</v>
       </c>
       <c r="F45" s="3">
+        <v>500</v>
+      </c>
+      <c r="G45" s="3">
+        <v>500</v>
+      </c>
+      <c r="H45" s="3">
         <v>300</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>300</v>
       </c>
-      <c r="H45" s="3">
-        <v>1700</v>
-      </c>
-      <c r="I45" s="3">
-        <v>1700</v>
-      </c>
       <c r="J45" s="3">
-        <v>1600</v>
+        <v>1400</v>
       </c>
       <c r="K45" s="3">
         <v>1600</v>
@@ -3106,10 +3111,10 @@
         <v>17000</v>
       </c>
       <c r="F46" s="3">
-        <v>18700</v>
+        <v>19100</v>
       </c>
       <c r="G46" s="3">
-        <v>18700</v>
+        <v>19100</v>
       </c>
       <c r="H46" s="3">
         <v>18700</v>
@@ -3118,7 +3123,7 @@
         <v>18700</v>
       </c>
       <c r="J46" s="3">
-        <v>22700</v>
+        <v>16700</v>
       </c>
       <c r="K46" s="3">
         <v>22700</v>
@@ -3177,19 +3182,19 @@
         <v>1200</v>
       </c>
       <c r="F47" s="3">
+        <v>1200</v>
+      </c>
+      <c r="G47" s="3">
+        <v>1200</v>
+      </c>
+      <c r="H47" s="3">
         <v>1100</v>
       </c>
-      <c r="G47" s="3">
+      <c r="I47" s="3">
         <v>1100</v>
       </c>
-      <c r="H47" s="3">
-        <v>1300</v>
-      </c>
-      <c r="I47" s="3">
-        <v>1300</v>
-      </c>
       <c r="J47" s="3">
-        <v>1300</v>
+        <v>1100</v>
       </c>
       <c r="K47" s="3">
         <v>1300</v>
@@ -3248,19 +3253,19 @@
         <v>5900</v>
       </c>
       <c r="F48" s="3">
+        <v>5900</v>
+      </c>
+      <c r="G48" s="3">
+        <v>5900</v>
+      </c>
+      <c r="H48" s="3">
         <v>6000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>6000</v>
       </c>
-      <c r="H48" s="3">
-        <v>4000</v>
-      </c>
-      <c r="I48" s="3">
-        <v>4000</v>
-      </c>
       <c r="J48" s="3">
-        <v>5600</v>
+        <v>5800</v>
       </c>
       <c r="K48" s="3">
         <v>5600</v>
@@ -3331,7 +3336,7 @@
         <v>0</v>
       </c>
       <c r="J49" s="3">
-        <v>6700</v>
+        <v>0</v>
       </c>
       <c r="K49" s="3">
         <v>6700</v>
@@ -3543,8 +3548,8 @@
       <c r="I52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J52" s="3">
-        <v>500</v>
+      <c r="J52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K52" s="3">
         <v>500</v>
@@ -3674,19 +3679,19 @@
         <v>24100</v>
       </c>
       <c r="F54" s="3">
+        <v>26300</v>
+      </c>
+      <c r="G54" s="3">
+        <v>26300</v>
+      </c>
+      <c r="H54" s="3">
         <v>25900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>25900</v>
       </c>
-      <c r="H54" s="3">
-        <v>24400</v>
-      </c>
-      <c r="I54" s="3">
-        <v>24400</v>
-      </c>
       <c r="J54" s="3">
-        <v>38600</v>
+        <v>24000</v>
       </c>
       <c r="K54" s="3">
         <v>38600</v>
@@ -3799,19 +3804,19 @@
         <v>500</v>
       </c>
       <c r="F57" s="3">
+        <v>900</v>
+      </c>
+      <c r="G57" s="3">
+        <v>900</v>
+      </c>
+      <c r="H57" s="3">
         <v>500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>500</v>
       </c>
-      <c r="H57" s="3">
-        <v>700</v>
-      </c>
-      <c r="I57" s="3">
-        <v>700</v>
-      </c>
       <c r="J57" s="3">
-        <v>100</v>
+        <v>1200</v>
       </c>
       <c r="K57" s="3">
         <v>100</v>
@@ -3876,13 +3881,13 @@
         <v>0</v>
       </c>
       <c r="H58" s="3">
+        <v>0</v>
+      </c>
+      <c r="I58" s="3">
+        <v>0</v>
+      </c>
+      <c r="J58" s="3">
         <v>200</v>
-      </c>
-      <c r="I58" s="3">
-        <v>200</v>
-      </c>
-      <c r="J58" s="3">
-        <v>500</v>
       </c>
       <c r="K58" s="3">
         <v>500</v>
@@ -3941,19 +3946,19 @@
         <v>200</v>
       </c>
       <c r="F59" s="3">
+        <v>1100</v>
+      </c>
+      <c r="G59" s="3">
+        <v>1100</v>
+      </c>
+      <c r="H59" s="3">
         <v>400</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>400</v>
       </c>
-      <c r="H59" s="3">
-        <v>1000</v>
-      </c>
-      <c r="I59" s="3">
-        <v>1000</v>
-      </c>
       <c r="J59" s="3">
-        <v>2900</v>
+        <v>500</v>
       </c>
       <c r="K59" s="3">
         <v>2900</v>
@@ -4012,19 +4017,19 @@
         <v>1500</v>
       </c>
       <c r="F60" s="3">
+        <v>2300</v>
+      </c>
+      <c r="G60" s="3">
+        <v>2300</v>
+      </c>
+      <c r="H60" s="3">
         <v>1500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>1500</v>
       </c>
-      <c r="H60" s="3">
-        <v>2700</v>
-      </c>
-      <c r="I60" s="3">
-        <v>2700</v>
-      </c>
       <c r="J60" s="3">
-        <v>4200</v>
+        <v>2800</v>
       </c>
       <c r="K60" s="3">
         <v>4200</v>
@@ -4089,13 +4094,13 @@
         <v>0</v>
       </c>
       <c r="H61" s="3">
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="I61" s="3">
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="J61" s="3">
-        <v>1200</v>
+        <v>500</v>
       </c>
       <c r="K61" s="3">
         <v>1200</v>
@@ -4438,19 +4443,19 @@
         <v>1500</v>
       </c>
       <c r="F66" s="3">
+        <v>2600</v>
+      </c>
+      <c r="G66" s="3">
+        <v>2600</v>
+      </c>
+      <c r="H66" s="3">
         <v>1700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>1700</v>
       </c>
-      <c r="H66" s="3">
-        <v>3400</v>
-      </c>
-      <c r="I66" s="3">
-        <v>3400</v>
-      </c>
       <c r="J66" s="3">
-        <v>5600</v>
+        <v>3300</v>
       </c>
       <c r="K66" s="3">
         <v>5600</v>
@@ -4820,19 +4825,19 @@
         <v>-12900</v>
       </c>
       <c r="F72" s="3">
+        <v>-7500</v>
+      </c>
+      <c r="G72" s="3">
+        <v>-7500</v>
+      </c>
+      <c r="H72" s="3">
         <v>-6500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-6500</v>
       </c>
-      <c r="H72" s="3">
-        <v>-5900</v>
-      </c>
-      <c r="I72" s="3">
-        <v>-5900</v>
-      </c>
       <c r="J72" s="3">
-        <v>5400</v>
+        <v>-5800</v>
       </c>
       <c r="K72" s="3">
         <v>5400</v>
@@ -5104,19 +5109,19 @@
         <v>18600</v>
       </c>
       <c r="F76" s="3">
+        <v>20300</v>
+      </c>
+      <c r="G76" s="3">
+        <v>20300</v>
+      </c>
+      <c r="H76" s="3">
         <v>20800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>20800</v>
       </c>
-      <c r="H76" s="3">
-        <v>18000</v>
-      </c>
-      <c r="I76" s="3">
-        <v>18000</v>
-      </c>
       <c r="J76" s="3">
-        <v>29900</v>
+        <v>17700</v>
       </c>
       <c r="K76" s="3">
         <v>29900</v>
@@ -5251,19 +5256,19 @@
         <v>45930</v>
       </c>
       <c r="F80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="G80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="H80" s="2">
         <v>45657</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45565</v>
       </c>
-      <c r="H80" s="2">
-        <v>45291</v>
-      </c>
-      <c r="I80" s="2">
-        <v>45199</v>
-      </c>
       <c r="J80" s="2">
-        <v>44926</v>
+        <v>45473</v>
       </c>
       <c r="K80" s="2">
         <v>44834</v>
@@ -5322,19 +5327,19 @@
         <v>-2700</v>
       </c>
       <c r="F81" s="3">
+        <v>-500</v>
+      </c>
+      <c r="G81" s="3">
+        <v>-500</v>
+      </c>
+      <c r="H81" s="3">
         <v>-400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>-400</v>
       </c>
-      <c r="H81" s="3">
-        <v>-3300</v>
-      </c>
-      <c r="I81" s="3">
-        <v>-3300</v>
-      </c>
       <c r="J81" s="3">
-        <v>-1500</v>
+        <v>0</v>
       </c>
       <c r="K81" s="3">
         <v>-1500</v>
@@ -5414,10 +5419,10 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F83" s="3">
         <v>100</v>
@@ -5426,10 +5431,10 @@
         <v>100</v>
       </c>
       <c r="H83" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="I83" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="J83" s="3">
         <v>100</v>
@@ -5846,19 +5851,19 @@
         <v>-500</v>
       </c>
       <c r="F89" s="3">
+        <v>900</v>
+      </c>
+      <c r="G89" s="3">
+        <v>900</v>
+      </c>
+      <c r="H89" s="3">
         <v>-1100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>-1100</v>
       </c>
-      <c r="H89" s="3">
-        <v>1000</v>
-      </c>
-      <c r="I89" s="3">
-        <v>1000</v>
-      </c>
       <c r="J89" s="3">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="K89" s="3">
         <v>100</v>
@@ -5943,20 +5948,20 @@
       <c r="E91" s="3">
         <v>-100</v>
       </c>
-      <c r="F91" s="3">
+      <c r="F91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H91" s="3">
         <v>-500</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-500</v>
       </c>
-      <c r="H91" s="3">
-        <v>-400</v>
-      </c>
-      <c r="I91" s="3">
-        <v>-400</v>
-      </c>
       <c r="J91" s="3">
-        <v>-900</v>
+        <v>-1000</v>
       </c>
       <c r="K91" s="3">
         <v>-900</v>
@@ -6157,19 +6162,19 @@
         <v>100</v>
       </c>
       <c r="F94" s="3">
-        <v>0</v>
+        <v>-500</v>
       </c>
       <c r="G94" s="3">
-        <v>0</v>
+        <v>-500</v>
       </c>
       <c r="H94" s="3">
-        <v>-2800</v>
+        <v>0</v>
       </c>
       <c r="I94" s="3">
-        <v>-2800</v>
+        <v>0</v>
       </c>
       <c r="J94" s="3">
-        <v>-100</v>
+        <v>-900</v>
       </c>
       <c r="K94" s="3">
         <v>-100</v>
@@ -6538,20 +6543,20 @@
       <c r="E100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F100" s="3">
+      <c r="F100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H100" s="3">
         <v>1900</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>1900</v>
       </c>
-      <c r="H100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J100" s="3">
-        <v>0</v>
+      <c r="J100" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K100" s="3">
         <v>0</v>
@@ -6610,10 +6615,10 @@
         <v>0</v>
       </c>
       <c r="F101" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="G101" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H101" s="3">
         <v>0</v>
@@ -6681,19 +6686,19 @@
         <v>-400</v>
       </c>
       <c r="F102" s="3">
+        <v>500</v>
+      </c>
+      <c r="G102" s="3">
+        <v>500</v>
+      </c>
+      <c r="H102" s="3">
         <v>800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>800</v>
       </c>
-      <c r="H102" s="3">
-        <v>-1900</v>
-      </c>
-      <c r="I102" s="3">
-        <v>-1900</v>
-      </c>
       <c r="J102" s="3">
-        <v>0</v>
+        <v>-600</v>
       </c>
       <c r="K102" s="3">
         <v>0</v>
